--- a/import/user_import.xlsx
+++ b/import/user_import.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Новая папка (2)\Пример\import\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arzam\OneDrive\Рабочий стол\exxx\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8258C3E4-8D8B-4BAF-8846-352759D9E799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="2136" windowWidth="26760" windowHeight="16560"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -22,15 +23,41 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
   <si>
     <t>Роль сотрудника</t>
   </si>
@@ -77,6 +104,123 @@
     <t>JlFRCZ</t>
   </si>
   <si>
+    <t>94d5ous@gmail.com</t>
+  </si>
+  <si>
+    <t>uth4iz@mail.com</t>
+  </si>
+  <si>
+    <t>5d4zbu@tutanota.com</t>
+  </si>
+  <si>
+    <t>ptec8ym@yahoo.com</t>
+  </si>
+  <si>
+    <t>1qz4kw@mail.com</t>
+  </si>
+  <si>
+    <t>4np6se@mail.com</t>
+  </si>
+  <si>
+    <t>yzls62@outlook.com</t>
+  </si>
+  <si>
+    <t>1diph5e@tutanota.com</t>
+  </si>
+  <si>
+    <t>tjde7c@yahoo.com</t>
+  </si>
+  <si>
+    <t>wpmrc3do@tutanota.com</t>
+  </si>
+  <si>
+    <t>Менеджер</t>
+  </si>
+  <si>
+    <t>Авторизированный клиент</t>
+  </si>
+  <si>
+    <t>Роль</t>
+  </si>
+  <si>
+    <t>Фамилия</t>
+  </si>
+  <si>
+    <t>Имя</t>
+  </si>
+  <si>
+    <t>Отчество</t>
+  </si>
+  <si>
+    <t>Никифорова</t>
+  </si>
+  <si>
+    <t>Весения</t>
+  </si>
+  <si>
+    <t>Николаевна</t>
+  </si>
+  <si>
+    <t>Сазонов</t>
+  </si>
+  <si>
+    <t>Руслан</t>
+  </si>
+  <si>
+    <t>Германович</t>
+  </si>
+  <si>
+    <t>Одинцов</t>
+  </si>
+  <si>
+    <t>Серафим</t>
+  </si>
+  <si>
+    <t>Артёмович</t>
+  </si>
+  <si>
+    <t>Степанов</t>
+  </si>
+  <si>
+    <t>Михаил</t>
+  </si>
+  <si>
+    <t>Ворсин</t>
+  </si>
+  <si>
+    <t>Петр</t>
+  </si>
+  <si>
+    <t>Евгеньевич</t>
+  </si>
+  <si>
+    <t>Старикова</t>
+  </si>
+  <si>
+    <t>Елена</t>
+  </si>
+  <si>
+    <t>Павловна</t>
+  </si>
+  <si>
+    <t>Михайлюк</t>
+  </si>
+  <si>
+    <t>Анна</t>
+  </si>
+  <si>
+    <t>Вячеславовна</t>
+  </si>
+  <si>
+    <t>Ситдикова</t>
+  </si>
+  <si>
+    <t>Анатольевна</t>
+  </si>
+  <si>
+    <t>Никифорова Весения Николаевна</t>
+  </si>
+  <si>
     <t>Сазонов Руслан Германович</t>
   </si>
   <si>
@@ -86,62 +230,23 @@
     <t>Степанов Михаил Артёмович</t>
   </si>
   <si>
+    <t>Ворсин Петр Евгеньевич</t>
+  </si>
+  <si>
+    <t>Старикова Елена Павловна</t>
+  </si>
+  <si>
     <t>Михайлюк Анна Вячеславовна</t>
   </si>
   <si>
     <t>Ситдикова Елена Анатольевна</t>
-  </si>
-  <si>
-    <t>Ворсин Петр Евгеньевич</t>
-  </si>
-  <si>
-    <t>Старикова Елена Павловна</t>
-  </si>
-  <si>
-    <t>Никифорова Весения Николаевна</t>
-  </si>
-  <si>
-    <t>94d5ous@gmail.com</t>
-  </si>
-  <si>
-    <t>uth4iz@mail.com</t>
-  </si>
-  <si>
-    <t>5d4zbu@tutanota.com</t>
-  </si>
-  <si>
-    <t>ptec8ym@yahoo.com</t>
-  </si>
-  <si>
-    <t>1qz4kw@mail.com</t>
-  </si>
-  <si>
-    <t>4np6se@mail.com</t>
-  </si>
-  <si>
-    <t>yzls62@outlook.com</t>
-  </si>
-  <si>
-    <t>1diph5e@tutanota.com</t>
-  </si>
-  <si>
-    <t>tjde7c@yahoo.com</t>
-  </si>
-  <si>
-    <t>wpmrc3do@tutanota.com</t>
-  </si>
-  <si>
-    <t>Менеджер</t>
-  </si>
-  <si>
-    <t>Авторизированный клиент</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -167,6 +272,13 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -200,7 +312,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -209,6 +321,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -525,16 +643,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.796875" customWidth="1"/>
+    <col min="1" max="1" width="24.75" customWidth="1"/>
     <col min="2" max="2" width="38.5" customWidth="1"/>
     <col min="3" max="3" width="36.5" customWidth="1"/>
+    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -547,172 +668,492 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" t="str" cm="1">
+        <f t="array" ref="H2:H4">_xlfn.UNIQUE(A2:A11)</f>
+        <v>Администратор</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Менеджер</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Авторизированный клиент</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="I19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="I24" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+      <c r="D25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <v>9</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26" t="s">
+        <v>57</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <v>10</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+      <c r="D27" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B13" s="1"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B14" s="1"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B16" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1"/>
-    <hyperlink ref="C3" r:id="rId2"/>
-    <hyperlink ref="C4" r:id="rId3"/>
-    <hyperlink ref="C5" r:id="rId4"/>
-    <hyperlink ref="C6" r:id="rId5"/>
-    <hyperlink ref="C7" r:id="rId6"/>
-    <hyperlink ref="C8" r:id="rId7"/>
-    <hyperlink ref="C9" r:id="rId8"/>
-    <hyperlink ref="C10" r:id="rId9"/>
-    <hyperlink ref="C11" r:id="rId10"/>
+    <hyperlink ref="C2" r:id="rId1" display="94d5ous@gmail.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C3" r:id="rId2" display="uth4iz@mail.com" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C4" r:id="rId3" display="yzls62@outlook.com" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C5" r:id="rId4" display="1diph5e@tutanota.com" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C6" r:id="rId5" display="tjde7c@yahoo.com" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="C7" r:id="rId6" display="wpmrc3do@tutanota.com" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="C8" r:id="rId7" display="5d4zbu@tutanota.com" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="C9" r:id="rId8" display="ptec8ym@yahoo.com" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="C10" r:id="rId9" display="1qz4kw@mail.com" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="C11" r:id="rId10" display="4np6se@mail.com" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="H18" r:id="rId11" xr:uid="{3F7C0ADD-AB5C-4376-9325-F492FE7224CA}"/>
+    <hyperlink ref="H19" r:id="rId12" xr:uid="{16ECE7F5-7146-4EE7-9EC4-55AE515C010D}"/>
+    <hyperlink ref="H20" r:id="rId13" xr:uid="{78A205DC-0D67-4D98-A47F-EDC478C46EB7}"/>
+    <hyperlink ref="H21" r:id="rId14" xr:uid="{4EB1D2CA-5786-4A65-ADC2-CBC9803EABA1}"/>
+    <hyperlink ref="H22" r:id="rId15" xr:uid="{F9F928B2-EF7E-4788-B5C6-81B54A4B1C29}"/>
+    <hyperlink ref="H23" r:id="rId16" xr:uid="{390DB527-6CC2-49F6-9A8D-A8716742EBF9}"/>
+    <hyperlink ref="H24" r:id="rId17" xr:uid="{32A6C9A7-8EDE-446A-B7A1-3283CD3C275B}"/>
+    <hyperlink ref="H25" r:id="rId18" xr:uid="{1FC5F587-8BF8-4AC1-9EA5-B21BA115D8E7}"/>
+    <hyperlink ref="H26" r:id="rId19" xr:uid="{BA184764-8DA3-4423-9727-373BE3EB64BB}"/>
+    <hyperlink ref="H27" r:id="rId20" xr:uid="{7F4B0A0D-B5A3-40EF-9EDF-FE2FE206139C}"/>
+    <hyperlink ref="F18" r:id="rId21" display="94d5ous@gmail.com" xr:uid="{C785349E-72D3-431E-8726-309642709999}"/>
+    <hyperlink ref="F19" r:id="rId22" display="uth4iz@mail.com" xr:uid="{79846FB5-9767-4658-B6EB-830CDC9D87A7}"/>
+    <hyperlink ref="F20" r:id="rId23" display="yzls62@outlook.com" xr:uid="{29A5DE77-0645-4E61-AC3A-3BCEBDFCB73A}"/>
+    <hyperlink ref="F21" r:id="rId24" display="1diph5e@tutanota.com" xr:uid="{26164425-7D86-4CE8-83CA-D98690CDD02F}"/>
+    <hyperlink ref="F22" r:id="rId25" display="tjde7c@yahoo.com" xr:uid="{AE444AE1-1C21-466B-8A87-A5CA07C3C9BB}"/>
+    <hyperlink ref="F23" r:id="rId26" display="wpmrc3do@tutanota.com" xr:uid="{21AC5B61-9112-483F-8250-264FD59086D3}"/>
+    <hyperlink ref="F24" r:id="rId27" display="5d4zbu@tutanota.com" xr:uid="{F508E382-531A-445F-8D87-6CB793246FAA}"/>
+    <hyperlink ref="F25" r:id="rId28" display="ptec8ym@yahoo.com" xr:uid="{CB71DCE5-74F6-4560-AE99-82ABDD20AA7D}"/>
+    <hyperlink ref="F26" r:id="rId29" display="1qz4kw@mail.com" xr:uid="{D963AE2F-ABD0-4F53-AE5D-BD312AF1A256}"/>
+    <hyperlink ref="F27" r:id="rId30" display="4np6se@mail.com" xr:uid="{B396CA8D-FBC1-4246-8F37-7495C7123A2E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>
 </worksheet>
 </file>